--- a/hiring_companies_2026-10-25.xlsx
+++ b/hiring_companies_2026-10-25.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WD.ai</t>
+          <t>DirectEmployers Association</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,12 +492,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Software Developer - Java/C#</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7690055940645289962</t>
+          <t>https://jooble.org/jdp/-4505851101932507319</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=WD.ai</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DirectEmployers+Association</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WD.ai</t>
+          <t>DirectEmployers Association</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Software Developer - Java/C#</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7690055940645289962</t>
+          <t>https://jooble.org/jdp/-4505851101932507319</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=WD.ai</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DirectEmployers+Association</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WD.ai</t>
+          <t>DirectEmployers Association</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Software Developer - Java/C#</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7690055940645289962</t>
+          <t>https://jooble.org/jdp/-4505851101932507319</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=WD.ai</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DirectEmployers+Association</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WD.ai</t>
+          <t>DirectEmployers Association</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Software Developer - Java/C#</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7690055940645289962</t>
+          <t>https://jooble.org/jdp/-4505851101932507319</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=WD.ai</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DirectEmployers+Association</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WD.ai</t>
+          <t>DirectEmployers Association</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Software Developer - Java/C#</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7690055940645289962</t>
+          <t>https://jooble.org/jdp/-4505851101932507319</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=WD.ai</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DirectEmployers+Association</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WD.ai</t>
+          <t>DirectEmployers Association</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Web Designer</t>
+          <t>Software Developer - Java/C#</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7690055940645289962</t>
+          <t>https://jooble.org/jdp/-4505851101932507319</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=WD.ai</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DirectEmployers+Association</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tonic3</t>
+          <t>Turing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Copywriter | Motion Graphics Designer</t>
+          <t>Remote Python/Typescript Engineer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8901782824795861618</t>
+          <t>https://jooble.org/jdp/-2248583855414712069</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tonic3</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Turing</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tonic3</t>
+          <t>Turing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Copywriter | Motion Graphics Designer</t>
+          <t>Remote Python/Typescript Engineer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8901782824795861618</t>
+          <t>https://jooble.org/jdp/-2248583855414712069</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tonic3</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Turing</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tonic3</t>
+          <t>Turing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Copywriter | Motion Graphics Designer</t>
+          <t>Remote Python/Typescript Engineer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8901782824795861618</t>
+          <t>https://jooble.org/jdp/-8899323062064409909</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tonic3</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Turing</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tonic3</t>
+          <t>Turing</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Copywriter | Motion Graphics Designer</t>
+          <t>Remote Python/Typescript Engineer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8901782824795861618</t>
+          <t>https://jooble.org/jdp/-8899323062064409909</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tonic3</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Turing</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tonic3</t>
+          <t>Turing</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Copywriter | Motion Graphics Designer</t>
+          <t>Remote Python/Typescript Engineer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8901782824795861618</t>
+          <t>https://jooble.org/jdp/-8899323062064409909</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tonic3</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Turing</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tonic3</t>
+          <t>Turing</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Copywriter | Motion Graphics Designer</t>
+          <t>Remote Python/Typescript Engineer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8901782824795861618</t>
+          <t>https://jooble.org/jdp/-8899323062064409909</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tonic3</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Turing</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CornerStone Professional Placement</t>
+          <t>Ez Health</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Marketing Strategist</t>
+          <t>Sales Representative (Fully Remote)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2070141606160905521</t>
+          <t>https://jooble.org/jdp/5626025073495641961</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CornerStone+Professional+Placement</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ez+Health</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CornerStone Professional Placement</t>
+          <t>Ez Health</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Marketing Strategist</t>
+          <t>Sales Representative (Fully Remote)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2070141606160905521</t>
+          <t>https://jooble.org/jdp/5626025073495641961</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CornerStone+Professional+Placement</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ez+Health</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CornerStone Professional Placement</t>
+          <t>Ez Health</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Marketing Strategist</t>
+          <t>Sales Representative (Fully Remote)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2070141606160905521</t>
+          <t>https://jooble.org/jdp/5626025073495641961</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CornerStone+Professional+Placement</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ez+Health</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CornerStone Professional Placement</t>
+          <t>Ez Health</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Marketing Strategist</t>
+          <t>Sales Representative (Fully Remote)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2070141606160905521</t>
+          <t>https://jooble.org/jdp/5626025073495641961</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CornerStone+Professional+Placement</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ez+Health</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CornerStone Professional Placement</t>
+          <t>Ez Health</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Marketing Strategist</t>
+          <t>Sales Representative (Fully Remote)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2070141606160905521</t>
+          <t>https://jooble.org/jdp/5626025073495641961</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CornerStone+Professional+Placement</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ez+Health</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CornerStone Professional Placement</t>
+          <t>Ez Health</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Marketing Strategist</t>
+          <t>Sales Representative (Fully Remote)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2070141606160905521</t>
+          <t>https://jooble.org/jdp/5626025073495641961</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=CornerStone+Professional+Placement</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ez+Health</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kavaliro</t>
+          <t>Syneos Health Inc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dynamics 365 Marketing Director</t>
+          <t>Remote Pharmaceutical Sales Specialist</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3892589660178266413</t>
+          <t>https://jooble.org/jdp/7012403027070971468</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kavaliro</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Syneos+Health+Inc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kavaliro</t>
+          <t>Syneos Health Inc</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1385,22 +1385,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dynamics 365 Marketing Director</t>
+          <t>Remote Pharmaceutical Sales Specialist</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3892589660178266413</t>
+          <t>https://jooble.org/jdp/7012403027070971468</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kavaliro</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Syneos+Health+Inc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kavaliro</t>
+          <t>The Edson Agency</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dynamics 365 Marketing Director</t>
+          <t>Remote Sales Representative</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3892589660178266413</t>
+          <t>https://jooble.org/jdp/3154709070626142869</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kavaliro</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Edson+Agency</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kavaliro</t>
+          <t>Syneos Health Inc</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1479,22 +1479,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dynamics 365 Marketing Director</t>
+          <t>Remote Pharmaceutical Sales Specialist</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3892589660178266413</t>
+          <t>https://jooble.org/jdp/7012403027070971468</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kavaliro</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Syneos+Health+Inc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kavaliro</t>
+          <t>Syneos Health Inc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1526,22 +1526,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Dynamics 365 Marketing Director</t>
+          <t>Remote Pharmaceutical Sales Specialist</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3892589660178266413</t>
+          <t>https://jooble.org/jdp/7012403027070971468</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kavaliro</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Syneos+Health+Inc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kavaliro</t>
+          <t>The Edson Agency</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Dynamics 365 Marketing Director</t>
+          <t>Remote Sales Representative</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3892589660178266413</t>
+          <t>https://jooble.org/jdp/6452962736164786847</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kavaliro</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Edson+Agency</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Network Solutions</t>
+          <t>Remote Work &amp; Working at Home Jobs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1620,22 +1620,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Marketing Coordinator</t>
+          <t>Sr. Writer - Creative Agency - Remote</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4959425932849598811</t>
+          <t>https://jooble.org/jdp/-5422126467539216131</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IT+Network+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Remote+Work+%26+Working+at+Home+Jobs</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Network Solutions</t>
+          <t>Remote Work &amp; Working at Home Jobs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1667,22 +1667,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Marketing Coordinator</t>
+          <t>Sr. Writer - Creative Agency - Remote</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4959425932849598811</t>
+          <t>https://jooble.org/jdp/-5422126467539216131</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IT+Network+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Remote+Work+%26+Working+at+Home+Jobs</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Network Solutions</t>
+          <t>Syneos Health Inc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1714,22 +1714,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Marketing Coordinator</t>
+          <t>Remote Pharmaceutical Sales Specialist</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4959425932849598811</t>
+          <t>https://jooble.org/jdp/7012403027070971468</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IT+Network+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Syneos+Health+Inc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Network Solutions</t>
+          <t>Remote Work &amp; Working at Home Jobs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1761,22 +1761,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Marketing Coordinator</t>
+          <t>Sr. Writer - Creative Agency - Remote</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4959425932849598811</t>
+          <t>https://jooble.org/jdp/-5422126467539216131</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IT+Network+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Remote+Work+%26+Working+at+Home+Jobs</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QNY Creative</t>
+          <t>Remote Work &amp; Working at Home Jobs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1808,22 +1808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Amazon Advertising &amp; Paid Search Specialist Full Time</t>
+          <t>Sr. Writer - Creative Agency - Remote</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8983675093379580780</t>
+          <t>https://jooble.org/jdp/-5422126467539216131</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=QNY+Creative</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Remote+Work+%26+Working+at+Home+Jobs</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT Network Solutions</t>
+          <t>Calance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Marketing Coordinator</t>
+          <t>Cybersecurity Developer - hybrid (3 days onsite) | Golang Developer - hybrid (3 days onsite)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4959425932849598811</t>
+          <t>https://jooble.org/jdp/-815760062456587673</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IT+Network+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Calance</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QNY Creative</t>
+          <t>Claravine</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1902,22 +1902,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Amazon Advertising &amp; Paid Search Specialist Full Time</t>
+          <t>SVP of Marketing</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8983675093379580780</t>
+          <t>https://jooble.org/jdp/3165342609326973030</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=QNY+Creative</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Claravine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,7 +1934,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QNY Creative</t>
+          <t>Claravine</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1949,22 +1949,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Amazon Advertising &amp; Paid Search Specialist Full Time</t>
+          <t>SVP of Marketing</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8983675093379580780</t>
+          <t>https://jooble.org/jdp/3165342609326973030</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=QNY+Creative</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Claravine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QNY Creative</t>
+          <t>Remote Work &amp; Working at Home Jobs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1996,22 +1996,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Amazon Advertising &amp; Paid Search Specialist Full Time</t>
+          <t>Sr. Writer - Creative Agency - Remote</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8983675093379580780</t>
+          <t>https://jooble.org/jdp/-5422126467539216131</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=QNY+Creative</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Remote+Work+%26+Working+at+Home+Jobs</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QNY Creative</t>
+          <t>Claravine</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2043,22 +2043,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Amazon Advertising &amp; Paid Search Specialist Full Time</t>
+          <t>SVP of Marketing</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8983675093379580780</t>
+          <t>https://jooble.org/jdp/3165342609326973030</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=QNY+Creative</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Claravine</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT Network Solutions</t>
+          <t>Claravine</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Marketing Coordinator</t>
+          <t>SVP of Marketing</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4959425932849598811</t>
+          <t>https://jooble.org/jdp/3165342609326973030</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=IT+Network+Solutions</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Claravine</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QNY Creative</t>
+          <t>Syneos Health Inc</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2137,22 +2137,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Amazon Advertising &amp; Paid Search Specialist Full Time</t>
+          <t>Remote Pharmaceutical Sales Specialist</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/8983675093379580780</t>
+          <t>https://jooble.org/jdp/7012403027070971468</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=QNY+Creative</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Syneos+Health+Inc</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>The Sage Group</t>
+          <t>Custom Ink</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Director of Marketing Communications</t>
+          <t>CRM Marketing Coordinator</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6545373508467274166</t>
+          <t>https://jooble.org/jdp/-2767369196493727611</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Sage+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Custom+Ink</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,7 +2216,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>The Sage Group</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Director of Marketing Communications</t>
+          <t>Videographer</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6545373508467274166</t>
+          <t>https://jooble.org/jdp/-9120908391201707122</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Sage+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Trulieve</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,7 +2263,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The Sage Group</t>
+          <t>Claravine</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Director of Marketing Communications</t>
+          <t>SVP of Marketing</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6545373508467274166</t>
+          <t>https://jooble.org/jdp/3165342609326973030</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Sage+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Claravine</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>The Sage Group</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Director of Marketing Communications</t>
+          <t>Videographer</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6545373508467274166</t>
+          <t>https://jooble.org/jdp/-1992647874748208446</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Sage+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Trulieve</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>The Sage Group</t>
+          <t>Custom Ink</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,22 +2372,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Director of Marketing Communications</t>
+          <t>CRM Marketing Coordinator</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6545373508467274166</t>
+          <t>https://jooble.org/jdp/-2767369196493727611</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Sage+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Custom+Ink</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>The Sage Group</t>
+          <t>Remote Work &amp; Working at Home Jobs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Director of Marketing Communications</t>
+          <t>Sr. Writer - Creative Agency - Remote</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6545373508467274166</t>
+          <t>https://jooble.org/jdp/-5422126467539216131</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=The+Sage+Group</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Remote+Work+%26+Working+at+Home+Jobs</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Supreme Optimization</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Scientific Digital Marketing Strategist, Paid Ads (PhD Required)</t>
+          <t>Videographer</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2090085777126216441</t>
+          <t>https://jooble.org/jdp/8513408650515301494</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Supreme+Optimization</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Trulieve</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Supreme Optimization</t>
+          <t>Custom Ink</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Scientific Digital Marketing Strategist, Paid Ads (PhD Required)</t>
+          <t>CRM Marketing Coordinator</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2090085777126216441</t>
+          <t>https://jooble.org/jdp/-2767369196493727611</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Supreme+Optimization</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Custom+Ink</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Supreme Optimization</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Scientific Digital Marketing Strategist, Paid Ads (PhD Required)</t>
+          <t>Videographer</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2090085777126216441</t>
+          <t>https://jooble.org/jdp/-9120908391201707122</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Supreme+Optimization</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Trulieve</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Supreme Optimization</t>
+          <t>Custom Ink</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Scientific Digital Marketing Strategist, Paid Ads (PhD Required)</t>
+          <t>CRM Marketing Coordinator</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2090085777126216441</t>
+          <t>https://jooble.org/jdp/4923896146527154141</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Supreme+Optimization</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Custom+Ink</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Supreme Optimization</t>
+          <t>Trulieve</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Scientific Digital Marketing Strategist, Paid Ads (PhD Required)</t>
+          <t>Videographer</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2090085777126216441</t>
+          <t>https://jooble.org/jdp/8513408650515301494</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Supreme+Optimization</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Trulieve</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Supreme Optimization</t>
+          <t>Claravine</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Scientific Digital Marketing Strategist, Paid Ads (PhD Required)</t>
+          <t>SVP of Marketing</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/2090085777126216441</t>
+          <t>https://jooble.org/jdp/3165342609326973030</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Supreme+Optimization</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Claravine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Protecht</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Brand &amp; Creative Lead</t>
+          <t>Social Media Specialist, X</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4069611549547860840</t>
+          <t>https://jooble.org/jdp/379765821313518627</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Protecht</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Nebius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Protecht</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Brand &amp; Creative Lead</t>
+          <t>Social Media Specialist, X</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-4069611549547860840</t>
+          <t>https://jooble.org/jdp/379765821313518627</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Protecht</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Nebius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
